--- a/tools/excel/tisax/tisax-v5.1.xlsx
+++ b/tools/excel/tisax/tisax-v5.1.xlsx
@@ -1,16 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="library_content" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="controls" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="implementation_groups" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="library_meta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="controls_meta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="controls_content" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="scores_meta" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="scores_content" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="implementation_groups_meta" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="implementation_groups_content" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,93 +419,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>library_urn</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>urn:intuitem:risk:library:tisax-v5.1</t>
+          <t>library</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>library_version</t>
+          <t>urn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>urn:intuitem:risk:library:tisax-v5.1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>library_locale</t>
+          <t>version</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>library_ref_id</t>
+          <t>locale</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TISAX v5.1</t>
+          <t>en</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>library_name</t>
+          <t>ref_id</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trusted Information Security Assessment Exchange    </t>
+          <t>TISAX v5.1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>library_description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VDA ISA provides the basis for
+          <t>Trusted Information Security Assessment Exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VDA ISA provides the basis for
 - a self-assessment to determine the state of information security in an organization (e.g. company)
 - audits performed by internal departments (e.g. Internal Audit, Information Security)
 - a review in accordance with TISAX (Trusted Information Security Assessment Exchange, http://enx.com/tisax/)
-Source: https://portal.enx.com/isa5-en.xlsx
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>library_copyright</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+Source: https://portal.enx.com/isa5-en.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>copyright</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Publisher: VERBAND DER AUTOMOBILINDUSTRIE e. V. (VDA, German Association of the Automotive Industry); Behrenstr. 35; 10117 Berlin; www.vda.de
 © 2022 Verband der Automobilindustrie e.V., Berlin
@@ -510,151 +524,27 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>library_provider</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>VDA</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>library_packager</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>intuitem</t>
+          <t>VDA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>framework_urn</t>
+          <t>packager</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>urn:intuitem:risk:framework:tisax-v5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>framework_ref_id</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TISAX v5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>framework_name</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trusted Information Security Assessment Exchange</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>framework_description</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VDA ISA provides the basis for
-- a self-assessment to determine the state of information security in an organization (e.g. company)
-- audits performed by internal departments (e.g. Internal Audit, Information Security)
-- a review in accordance with TISAX (Trusted Information Security Assessment Exchange, http://enx.com/tisax/)
-Source: https://portal.enx.com/isa5-en.xlsx
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>framework_min_score</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>framework_max_score</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>tab</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>controls</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>requirements</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>tab</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>scores</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>scores</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>tab</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>implementation_groups</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>implementation_groups</t>
+          <t>intuitem</t>
         </is>
       </c>
     </row>
@@ -669,6 +559,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>base_urn</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>urn:intuitem:risk:req_node:tisax-v5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>urn</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>urn:intuitem:risk:framework:tisax-v5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ref_id</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TISAX v5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Trusted Information Security Assessment Exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VDA ISA provides the basis for
+- a self-assessment to determine the state of information security in an organization (e.g. company)
+- audits performed by internal departments (e.g. Internal Audit, Information Security)
+- a review in accordance with TISAX (Trusted Information Security Assessment Exchange, http://enx.com/tisax/)
+Source: https://portal.enx.com/isa5-en.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>min_score</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>max_score</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>scores_definition</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>implementation_groups_definition</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>implementation_groups</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -705,7 +733,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
         <v>1</v>
       </c>
@@ -719,11 +746,8 @@
           <t>IS Policies and Organization</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
         <v>2</v>
       </c>
@@ -732,16 +756,13 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Information Security Policies</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
         <v>3</v>
       </c>
@@ -750,13 +771,11 @@
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>To what extent are information security policies available?</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,7 +786,6 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -796,7 +814,6 @@
       <c r="B6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -820,7 +837,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
         <v>2</v>
       </c>
@@ -829,16 +845,13 @@
           <t>1.2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Organization of Information Security</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
         <v>3</v>
       </c>
@@ -847,13 +860,11 @@
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>To what extent is information security managed within the organization?</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -864,7 +875,6 @@
       <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -887,7 +897,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
         <v>3</v>
       </c>
@@ -896,13 +905,11 @@
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>To what extent are information security responsibilities organized?</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -913,7 +920,6 @@
       <c r="B11" t="n">
         <v>4</v>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -942,7 +948,6 @@
       <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -968,7 +973,6 @@
       <c r="B13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -986,7 +990,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
         <v>3</v>
       </c>
@@ -995,13 +998,11 @@
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>To what extent are information security requirements taken into account in projects?</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1012,7 +1013,6 @@
       <c r="B15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1038,7 +1038,6 @@
       <c r="B16" t="n">
         <v>4</v>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1066,7 +1065,6 @@
       <c r="B17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -1084,7 +1082,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
         <v>3</v>
       </c>
@@ -1093,13 +1090,11 @@
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>To what extent are the responsibilities between external IT service providers and the own organization defined?</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1110,7 +1105,6 @@
       <c r="B19" t="n">
         <v>4</v>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1140,7 +1134,6 @@
       <c r="B20" t="n">
         <v>4</v>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1167,7 +1160,6 @@
       <c r="B21" t="n">
         <v>4</v>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -1189,7 +1181,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
         <v>2</v>
       </c>
@@ -1198,16 +1189,13 @@
           <t>1.3</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Asset Management</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
         <v>3</v>
       </c>
@@ -1216,13 +1204,11 @@
           <t>1.3.1</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent are information assets identified and recorded? </t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1233,7 +1219,6 @@
       <c r="B24" t="n">
         <v>4</v>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1262,7 +1247,6 @@
       <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1282,7 +1266,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
         <v>3</v>
       </c>
@@ -1291,13 +1274,11 @@
           <t>1.3.2</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>To what extent are information assets classified and managed in terms of their protection needs?</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1308,7 +1289,6 @@
       <c r="B27" t="n">
         <v>4</v>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1336,7 +1316,6 @@
       <c r="B28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1354,7 +1333,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
         <v>3</v>
       </c>
@@ -1363,13 +1341,11 @@
           <t>1.3.3</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>To what extent is it ensured that only evaluated and approved external IT services are used for processing the organization’s information assets?</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1380,7 +1356,6 @@
       <c r="B30" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1409,7 +1384,6 @@
       <c r="B31" t="n">
         <v>4</v>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1431,7 +1405,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
         <v>2</v>
       </c>
@@ -1440,16 +1413,13 @@
           <t>1.4</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>IS Risk Management</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
         <v>3</v>
       </c>
@@ -1458,13 +1428,11 @@
           <t>1.4.1</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>To what extent are information security risks managed?</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1475,7 +1443,6 @@
       <c r="B34" t="n">
         <v>4</v>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1504,7 +1471,6 @@
       <c r="B35" t="n">
         <v>4</v>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1526,7 +1492,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
         <v>2</v>
       </c>
@@ -1535,16 +1500,13 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Assessments</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
         <v>3</v>
       </c>
@@ -1553,13 +1515,11 @@
           <t>1.5.1</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>To what extent is compliance with information security ensured in procedures and processes?</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1570,7 +1530,6 @@
       <c r="B38" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1600,7 +1559,6 @@
       <c r="B39" t="n">
         <v>4</v>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1618,7 +1576,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
         <v>3</v>
       </c>
@@ -1627,13 +1584,11 @@
           <t>1.5.2</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>To what extent is the ISMS reviewed by an independent authority?</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1644,7 +1599,6 @@
       <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1671,7 +1625,6 @@
       <c r="B42" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1689,7 +1642,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
         <v>2</v>
       </c>
@@ -1698,16 +1650,13 @@
           <t>1.6</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Incident Management</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
         <v>3</v>
       </c>
@@ -1716,13 +1665,11 @@
           <t>1.6.1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>To what extent are information security events processed?</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1733,7 +1680,6 @@
       <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1771,7 +1717,6 @@
       <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1798,7 +1743,6 @@
       <c r="B47" t="n">
         <v>4</v>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -1816,7 +1760,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
         <v>1</v>
       </c>
@@ -1830,11 +1773,8 @@
           <t>Human Resources</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
         <v>2</v>
       </c>
@@ -1843,13 +1783,11 @@
           <t>2.1.1</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>To what extent is the qualification of employees for sensitive work fields ensured?</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1860,7 +1798,6 @@
       <c r="B50" t="n">
         <v>3</v>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1888,7 +1825,6 @@
       <c r="B51" t="n">
         <v>3</v>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1907,7 +1843,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
         <v>2</v>
       </c>
@@ -1916,13 +1851,11 @@
           <t>2.1.2</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>To what extent is all staff contractually bound to comply with information security policies?</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1933,7 +1866,6 @@
       <c r="B53" t="n">
         <v>3</v>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -1960,7 +1892,6 @@
       <c r="B54" t="n">
         <v>3</v>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -1980,7 +1911,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
         <v>2</v>
       </c>
@@ -1989,13 +1919,11 @@
           <t>2.1.3</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>To what extent is staff made aware of and trained with respect to the risks arising from the handling of information?</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2006,7 +1934,6 @@
       <c r="B56" t="n">
         <v>3</v>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2032,7 +1959,6 @@
       <c r="B57" t="n">
         <v>3</v>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2062,7 +1988,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
         <v>2</v>
       </c>
@@ -2071,13 +1996,11 @@
           <t>2.1.4</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>To what extent is teleworking regulated?</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2088,7 +2011,6 @@
       <c r="B59" t="n">
         <v>3</v>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2119,7 +2041,6 @@
       <c r="B60" t="n">
         <v>3</v>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2148,7 +2069,6 @@
       <c r="B61" t="n">
         <v>3</v>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -2166,11 +2086,9 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
         <v>3</v>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>Further information</t>
@@ -2183,7 +2101,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
         <v>1</v>
       </c>
@@ -2197,11 +2114,8 @@
           <t>Physical Security and Business Continuity</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
         <v>2</v>
       </c>
@@ -2210,13 +2124,11 @@
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>To what extent are security zones managed to protect information assets?</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2227,7 +2139,6 @@
       <c r="B65" t="n">
         <v>3</v>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2257,7 +2168,6 @@
       <c r="B66" t="n">
         <v>3</v>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2287,7 +2197,6 @@
       <c r="B67" t="n">
         <v>3</v>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -2305,11 +2214,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
         <v>3</v>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>Further information</t>
@@ -2329,7 +2236,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
         <v>2</v>
       </c>
@@ -2338,13 +2244,11 @@
           <t>3.1.2</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>To what extent is information security ensured in exceptional situations?</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2355,7 +2259,6 @@
       <c r="B70" t="n">
         <v>3</v>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2384,7 +2287,6 @@
       <c r="B71" t="n">
         <v>3</v>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2410,7 +2312,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
         <v>2</v>
       </c>
@@ -2419,13 +2320,11 @@
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>To what extent is the handling of supporting assets managed?</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2436,7 +2335,6 @@
       <c r="B73" t="n">
         <v>3</v>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2462,7 +2360,6 @@
       <c r="B74" t="n">
         <v>3</v>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -2480,7 +2377,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
         <v>2</v>
       </c>
@@ -2489,13 +2385,11 @@
           <t>3.1.4</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>To what extent is the handling of mobile IT devices and mobile data storage devices managed?</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2506,7 +2400,6 @@
       <c r="B76" t="n">
         <v>3</v>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2535,7 +2428,6 @@
       <c r="B77" t="n">
         <v>3</v>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2562,7 +2454,6 @@
       <c r="B78" t="n">
         <v>3</v>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -2581,7 +2472,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
         <v>1</v>
       </c>
@@ -2595,11 +2485,8 @@
           <t>Identity and Access Management</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
         <v>2</v>
       </c>
@@ -2608,16 +2495,13 @@
           <t>4.1</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Identity Management</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
         <v>3</v>
       </c>
@@ -2626,13 +2510,11 @@
           <t>4.1.1</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>To what extent is the use of identification means managed?</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2643,7 +2525,6 @@
       <c r="B82" t="n">
         <v>4</v>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2673,7 +2554,6 @@
       <c r="B83" t="n">
         <v>4</v>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2699,7 +2579,6 @@
       <c r="B84" t="n">
         <v>4</v>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -2718,7 +2597,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
         <v>3</v>
       </c>
@@ -2727,13 +2605,11 @@
           <t>4.1.2</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>To what extent is the user access to network services, IT systems and IT applications secured?</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2744,7 +2620,6 @@
       <c r="B86" t="n">
         <v>4</v>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2771,7 +2646,6 @@
       <c r="B87" t="n">
         <v>4</v>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2799,7 +2673,6 @@
       <c r="B88" t="n">
         <v>4</v>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -2825,7 +2698,6 @@
       <c r="B89" t="n">
         <v>4</v>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>(for very high protection needs)</t>
@@ -2843,7 +2715,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
         <v>3</v>
       </c>
@@ -2852,13 +2723,11 @@
           <t>4.1.3</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent are user accounts and login information securely managed and applied? </t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2869,7 +2738,6 @@
       <c r="B91" t="n">
         <v>4</v>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -2909,7 +2777,6 @@
       <c r="B92" t="n">
         <v>4</v>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -2935,7 +2802,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
         <v>2</v>
       </c>
@@ -2944,16 +2810,13 @@
           <t>4.2</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Access Management</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
         <v>3</v>
       </c>
@@ -2962,13 +2825,11 @@
           <t>4.2.1</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>To what extent are access rights assigned and managed?</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2979,7 +2840,6 @@
       <c r="B95" t="n">
         <v>4</v>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3008,7 +2868,6 @@
       <c r="B96" t="n">
         <v>4</v>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3038,7 +2897,6 @@
       <c r="B97" t="n">
         <v>4</v>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -3064,7 +2922,6 @@
       <c r="B98" t="n">
         <v>4</v>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>(for very high protection needs)</t>
@@ -3085,11 +2942,9 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
         <v>4</v>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>Further information</t>
@@ -3102,7 +2957,6 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
         <v>1</v>
       </c>
@@ -3116,11 +2970,8 @@
           <t>IT Security / Cyber Security</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
         <v>2</v>
       </c>
@@ -3129,16 +2980,13 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Cryptography</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
         <v>3</v>
       </c>
@@ -3147,13 +2995,11 @@
           <t>5.1.1</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>To what extent is the use of cryptographic procedures managed?</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3164,7 +3010,6 @@
       <c r="B103" t="n">
         <v>4</v>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3191,7 +3036,6 @@
       <c r="B104" t="n">
         <v>4</v>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3222,7 +3066,6 @@
       <c r="B105" t="n">
         <v>4</v>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -3240,7 +3083,6 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
         <v>3</v>
       </c>
@@ -3249,13 +3091,11 @@
           <t>5.1.2</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>To what extent is information protected during transfer?</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3266,7 +3106,6 @@
       <c r="B107" t="n">
         <v>4</v>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3294,7 +3133,6 @@
       <c r="B108" t="n">
         <v>4</v>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3321,7 +3159,6 @@
       <c r="B109" t="n">
         <v>4</v>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -3348,7 +3185,6 @@
       <c r="B110" t="n">
         <v>4</v>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>(for very high protection needs)</t>
@@ -3366,7 +3202,6 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
         <v>2</v>
       </c>
@@ -3375,16 +3210,13 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Operations Security</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
         <v>3</v>
       </c>
@@ -3393,13 +3225,11 @@
           <t>5.2.1</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent are changes managed? </t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3410,7 +3240,6 @@
       <c r="B113" t="n">
         <v>4</v>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3436,7 +3265,6 @@
       <c r="B114" t="n">
         <v>4</v>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3465,7 +3293,6 @@
       <c r="B115" t="n">
         <v>4</v>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -3483,7 +3310,6 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
         <v>3</v>
       </c>
@@ -3492,13 +3318,11 @@
           <t>5.2.2</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>To what extent are development and testing environments separated from operational environments?</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3509,7 +3333,6 @@
       <c r="B117" t="n">
         <v>4</v>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3536,7 +3359,6 @@
       <c r="B118" t="n">
         <v>4</v>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3557,7 +3379,6 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
         <v>3</v>
       </c>
@@ -3566,13 +3387,11 @@
           <t>5.2.3</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>To what extent are IT systems protected against malware?</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3583,7 +3402,6 @@
       <c r="B120" t="n">
         <v>4</v>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3610,7 +3428,6 @@
       <c r="B121" t="n">
         <v>4</v>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3637,7 +3454,6 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
         <v>3</v>
       </c>
@@ -3646,13 +3462,11 @@
           <t>5.2.4</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>To what extent are event logs recorded and analyzed?</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3663,7 +3477,6 @@
       <c r="B123" t="n">
         <v>4</v>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3693,7 +3506,6 @@
       <c r="B124" t="n">
         <v>4</v>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3721,7 +3533,6 @@
       <c r="B125" t="n">
         <v>4</v>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -3748,7 +3559,6 @@
       <c r="B126" t="n">
         <v>4</v>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>(for very high protection needs)</t>
@@ -3766,7 +3576,6 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
         <v>3</v>
       </c>
@@ -3775,13 +3584,11 @@
           <t>5.2.5</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent are vulnerabilities identified and addressed? </t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3792,7 +3599,6 @@
       <c r="B128" t="n">
         <v>4</v>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3819,7 +3625,6 @@
       <c r="B129" t="n">
         <v>4</v>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3839,7 +3644,6 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
         <v>3</v>
       </c>
@@ -3848,13 +3652,11 @@
           <t>5.2.6</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>To what extent are IT systems technically checked (system audit)?</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3865,7 +3667,6 @@
       <c r="B131" t="n">
         <v>4</v>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3895,7 +3696,6 @@
       <c r="B132" t="n">
         <v>4</v>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -3916,7 +3716,6 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
         <v>3</v>
       </c>
@@ -3925,14 +3724,12 @@
           <t>5.2.7</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent is the network of the organization managed?
 </t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3943,7 +3740,6 @@
       <c r="B134" t="n">
         <v>4</v>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -3970,7 +3766,6 @@
       <c r="B135" t="n">
         <v>4</v>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4002,7 +3797,6 @@
       <c r="B136" t="n">
         <v>4</v>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -4022,7 +3816,6 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
         <v>2</v>
       </c>
@@ -4031,16 +3824,13 @@
           <t>5.3</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>System acquisitions, requirement management and development</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
         <v>3</v>
       </c>
@@ -4049,13 +3839,11 @@
           <t>5.3.1</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>To what extent is information security considered in new or further developed IT systems?</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4066,7 +3854,6 @@
       <c r="B139" t="n">
         <v>4</v>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4095,7 +3882,6 @@
       <c r="B140" t="n">
         <v>4</v>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4119,7 +3905,6 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
         <v>3</v>
       </c>
@@ -4128,13 +3913,11 @@
           <t>5.3.2</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>To what extent are requirements for network services defined?</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4145,7 +3928,6 @@
       <c r="B142" t="n">
         <v>4</v>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4171,7 +3953,6 @@
       <c r="B143" t="n">
         <v>4</v>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4199,7 +3980,6 @@
       <c r="B144" t="n">
         <v>4</v>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -4217,7 +3997,6 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
         <v>3</v>
       </c>
@@ -4226,13 +4005,11 @@
           <t>5.3.3</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent is the return and secure removal of information assets from external IT services regulated? </t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4243,7 +4020,6 @@
       <c r="B146" t="n">
         <v>4</v>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4269,7 +4045,6 @@
       <c r="B147" t="n">
         <v>4</v>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4287,7 +4062,6 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
         <v>3</v>
       </c>
@@ -4296,13 +4070,11 @@
           <t>5.3.4</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>To what extent is information protected in shared external IT services?</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4313,7 +4085,6 @@
       <c r="B149" t="n">
         <v>4</v>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4339,7 +4110,6 @@
       <c r="B150" t="n">
         <v>4</v>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4359,7 +4129,6 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
         <v>1</v>
       </c>
@@ -4373,11 +4142,8 @@
           <t>Supplier Relationships</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
         <v>2</v>
       </c>
@@ -4386,14 +4152,12 @@
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent is information security ensured among contractors and cooperation partners?
 </t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4404,7 +4168,6 @@
       <c r="B153" t="n">
         <v>3</v>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4433,7 +4196,6 @@
       <c r="B154" t="n">
         <v>3</v>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4460,7 +4222,6 @@
       <c r="B155" t="n">
         <v>3</v>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>(for high protection needs)</t>
@@ -4478,11 +4239,9 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
         <v>3</v>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>Further information</t>
@@ -4506,7 +4265,6 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
       <c r="B157" t="n">
         <v>2</v>
       </c>
@@ -4515,13 +4273,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>To what extent is non-disclosure regarding the exchange of information contractually agreed?</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4532,7 +4288,6 @@
       <c r="B158" t="n">
         <v>3</v>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4561,7 +4316,6 @@
       <c r="B159" t="n">
         <v>3</v>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4588,7 +4342,6 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
       <c r="B160" t="n">
         <v>1</v>
       </c>
@@ -4602,11 +4355,8 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
       <c r="B161" t="n">
         <v>2</v>
       </c>
@@ -4615,13 +4365,11 @@
           <t>7.1.1</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>To what extent is compliance with regulatory and contractual provisions ensured?</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4632,7 +4380,6 @@
       <c r="B162" t="n">
         <v>3</v>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4659,7 +4406,6 @@
       <c r="B163" t="n">
         <v>3</v>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4677,7 +4423,6 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
       <c r="B164" t="n">
         <v>2</v>
       </c>
@@ -4686,13 +4431,11 @@
           <t>7.1.2</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent is the protection of personally identifiable data taken into account when implementing information security? </t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4703,7 +4446,6 @@
       <c r="B165" t="n">
         <v>3</v>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4723,7 +4465,6 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
       <c r="B166" t="n">
         <v>1</v>
       </c>
@@ -4737,11 +4478,8 @@
           <t>Prototype Protection</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
       <c r="B167" t="n">
         <v>2</v>
       </c>
@@ -4750,16 +4488,13 @@
           <t>8.1</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Physical and Environmental Security</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
       <c r="B168" t="n">
         <v>3</v>
       </c>
@@ -4768,13 +4503,11 @@
           <t>8.1.1</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>To what extent is a security concept available describing minimum requirements regarding the physical and environmental security for prototype protection?</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4785,7 +4518,6 @@
       <c r="B169" t="n">
         <v>4</v>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4817,7 +4549,6 @@
       <c r="B170" t="n">
         <v>4</v>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4835,7 +4566,6 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
       <c r="B171" t="n">
         <v>3</v>
       </c>
@@ -4844,13 +4574,11 @@
           <t>8.1.2</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>To what extent is perimeter security existent preventing unauthorized access to protected property objects?</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4861,7 +4589,6 @@
       <c r="B172" t="n">
         <v>4</v>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4887,7 +4614,6 @@
       <c r="B173" t="n">
         <v>4</v>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4908,7 +4634,6 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
       <c r="B174" t="n">
         <v>3</v>
       </c>
@@ -4917,13 +4642,11 @@
           <t>8.1.3</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>To what extent is the outer skin of the protected buildings constructed such as to prevent removal or opening of outer-skin components using standard tools?</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4934,7 +4657,6 @@
       <c r="B175" t="n">
         <v>4</v>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -4960,7 +4682,6 @@
       <c r="B176" t="n">
         <v>4</v>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -4979,7 +4700,6 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
       <c r="B177" t="n">
         <v>3</v>
       </c>
@@ -4988,13 +4708,11 @@
           <t>8.1.4</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>To what extent is view and sight protection ensured in defined security areas?</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5005,7 +4723,6 @@
       <c r="B178" t="n">
         <v>4</v>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5031,7 +4748,6 @@
       <c r="B179" t="n">
         <v>4</v>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>(should)</t>
@@ -5058,7 +4774,6 @@
       <c r="B180" t="n">
         <v>4</v>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>(for vehicles classified as requiring protection)</t>
@@ -5076,7 +4791,6 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
       <c r="B181" t="n">
         <v>3</v>
       </c>
@@ -5085,13 +4799,11 @@
           <t>8.1.5</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>To what extent is the protection against unauthorized entry regulated in the form of access control?</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5102,7 +4814,6 @@
       <c r="B182" t="n">
         <v>4</v>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5131,7 +4842,6 @@
       <c r="B183" t="n">
         <v>4</v>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>(for vehicles classified as requiring protection)</t>
@@ -5149,7 +4859,6 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
       <c r="B184" t="n">
         <v>3</v>
       </c>
@@ -5158,13 +4867,11 @@
           <t>8.1.6</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>To what extent are the premises to be secured monitored for intrusion?</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5175,7 +4882,6 @@
       <c r="B185" t="n">
         <v>4</v>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5197,7 +4903,6 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
       <c r="B186" t="n">
         <v>3</v>
       </c>
@@ -5206,13 +4911,11 @@
           <t>8.1.7</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>To what extent is a documented visitor management in place?</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5223,7 +4926,6 @@
       <c r="B187" t="n">
         <v>4</v>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5244,7 +4946,6 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
       <c r="B188" t="n">
         <v>3</v>
       </c>
@@ -5253,13 +4954,11 @@
           <t>8.1.8</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>To what extent is on-site client segregation existent?</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5270,7 +4969,6 @@
       <c r="B189" t="n">
         <v>4</v>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5299,7 +4997,6 @@
       <c r="B190" t="n">
         <v>4</v>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>(for vehicles classified as requiring protection)</t>
@@ -5317,7 +5014,6 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
       <c r="B191" t="n">
         <v>2</v>
       </c>
@@ -5326,16 +5022,13 @@
           <t>8.2</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>Organizational Requirements</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
       <c r="B192" t="n">
         <v>3</v>
       </c>
@@ -5344,13 +5037,11 @@
           <t>8.2.1</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>To what extent are non-disclosure agreements/obligations existent according to the valid contractual law?</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5361,7 +5052,6 @@
       <c r="B193" t="n">
         <v>4</v>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5382,7 +5072,6 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr"/>
       <c r="B194" t="n">
         <v>3</v>
       </c>
@@ -5391,13 +5080,11 @@
           <t>8.2.2</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>To what extent are requirements for commissioning subcontractors known and fulfilled?</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5408,7 +5095,6 @@
       <c r="B195" t="n">
         <v>4</v>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5431,7 +5117,6 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
       <c r="B196" t="n">
         <v>3</v>
       </c>
@@ -5440,13 +5125,11 @@
           <t>8.2.3</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>To what extent do employees and project members evidently participate in training and awareness measures regarding the handling of prototypes?</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5457,7 +5140,6 @@
       <c r="B197" t="n">
         <v>4</v>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5481,7 +5163,6 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
       <c r="B198" t="n">
         <v>3</v>
       </c>
@@ -5490,13 +5171,11 @@
           <t>8.2.4</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>To what extent are security classifications of the project and the resulting security measures known?</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5507,7 +5186,6 @@
       <c r="B199" t="n">
         <v>4</v>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5527,7 +5205,6 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
       <c r="B200" t="n">
         <v>3</v>
       </c>
@@ -5536,13 +5213,11 @@
           <t>8.2.5</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>To what extent is a process defined for granting access to security areas?</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5553,7 +5228,6 @@
       <c r="B201" t="n">
         <v>4</v>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5573,7 +5247,6 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
       <c r="B202" t="n">
         <v>3</v>
       </c>
@@ -5582,13 +5255,11 @@
           <t>8.2.6</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>To what extent are regulations for image recording and handling of created image material existent?</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5599,7 +5270,6 @@
       <c r="B203" t="n">
         <v>4</v>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5621,7 +5291,6 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
       <c r="B204" t="n">
         <v>3</v>
       </c>
@@ -5630,13 +5299,11 @@
           <t>8.2.7</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>To what extent is a process for carrying along and using mobile video and photography devices in(to) defined security areas established?</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5647,7 +5314,6 @@
       <c r="B205" t="n">
         <v>4</v>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5666,7 +5332,6 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
       <c r="B206" t="n">
         <v>2</v>
       </c>
@@ -5675,16 +5340,13 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>Handling of vehicles, components and parts</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
       <c r="B207" t="n">
         <v>3</v>
       </c>
@@ -5693,13 +5355,11 @@
           <t>8.3.1</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>To what extent are transports of vehicles, components or parts classified as requiring protection arranged according to the customer requirements?</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5710,7 +5370,6 @@
       <c r="B208" t="n">
         <v>4</v>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5731,7 +5390,6 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
       <c r="B209" t="n">
         <v>3</v>
       </c>
@@ -5740,13 +5398,11 @@
           <t>8.3.2</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>To what extent is it ensured that vehicles, components and parts classified as requiring protection are parked/stored in accordance with customer requirements?</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5757,7 +5413,6 @@
       <c r="B210" t="n">
         <v>4</v>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5775,7 +5430,6 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr"/>
       <c r="B211" t="n">
         <v>2</v>
       </c>
@@ -5784,16 +5438,13 @@
           <t>8.4</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>Requirements for trial vehicles</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
       <c r="B212" t="n">
         <v>3</v>
       </c>
@@ -5802,13 +5453,11 @@
           <t>8.4.1</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>To what extent are the predefined camouflage regulations implemented by the project members?</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5819,7 +5468,6 @@
       <c r="B213" t="n">
         <v>4</v>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5839,7 +5487,6 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
       <c r="B214" t="n">
         <v>3</v>
       </c>
@@ -5848,13 +5495,11 @@
           <t>8.4.2</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>To what extent are measures for protecting approved test and trial grounds observed/implemented?</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5865,7 +5510,6 @@
       <c r="B215" t="n">
         <v>4</v>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5887,7 +5531,6 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
       <c r="B216" t="n">
         <v>3</v>
       </c>
@@ -5896,13 +5539,11 @@
           <t>8.4.3</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>To what extent are protective measures for approved test and trial drives in public observed/implemented?</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5913,7 +5554,6 @@
       <c r="B217" t="n">
         <v>4</v>
       </c>
-      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5933,7 +5573,6 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
       <c r="B218" t="n">
         <v>2</v>
       </c>
@@ -5942,16 +5581,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>Requirements for events and shootings</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
       <c r="B219" t="n">
         <v>3</v>
       </c>
@@ -5960,13 +5596,11 @@
           <t>8.5.1</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>To what extent are security requirements for presentations and events involving vehicles, components or parts classified as requiring protection known?</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5977,7 +5611,6 @@
       <c r="B220" t="n">
         <v>4</v>
       </c>
-      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -5998,7 +5631,6 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
       <c r="B221" t="n">
         <v>3</v>
       </c>
@@ -6007,13 +5639,11 @@
           <t>8.5.2</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>To what extent are the protective measures for film and photo shootings involving vehicles, components or parts classified as requiring protection known?</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6024,7 +5654,6 @@
       <c r="B222" t="n">
         <v>4</v>
       </c>
-      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -6046,7 +5675,6 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
       <c r="B223" t="n">
         <v>1</v>
       </c>
@@ -6060,11 +5688,8 @@
           <t>Data Protection</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
       <c r="B224" t="n">
         <v>2</v>
       </c>
@@ -6073,13 +5698,11 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>To what extent is the implementation of data protection organized?</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6090,7 +5713,6 @@
       <c r="B225" t="n">
         <v>3</v>
       </c>
-      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -6115,7 +5737,6 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
       <c r="B226" t="n">
         <v>2</v>
       </c>
@@ -6124,13 +5745,11 @@
           <t>9.2</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>To what extent are organizational measures taken in order to ensure that personally identifiable data is processed in conformance with legislation?</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6141,7 +5760,6 @@
       <c r="B227" t="n">
         <v>3</v>
       </c>
-      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -6172,7 +5790,6 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
       <c r="B228" t="n">
         <v>2</v>
       </c>
@@ -6181,13 +5798,11 @@
           <t>9.3</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>To what extent is it ensured that the internal processes or workflows are carried out according to the currently valid data protection regulations and that these are regularly subjected to a quality check?</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6198,7 +5813,6 @@
       <c r="B229" t="n">
         <v>3</v>
       </c>
-      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -6220,7 +5834,6 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
       <c r="B230" t="n">
         <v>2</v>
       </c>
@@ -6229,14 +5842,12 @@
           <t>9.4</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t xml:space="preserve">To what extent are the relevant processing procedures documented with regard to their admissibility according to data protection law?
 </t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6247,7 +5858,6 @@
       <c r="B231" t="n">
         <v>3</v>
       </c>
-      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>(must)</t>
@@ -6263,127 +5873,6 @@
       <c r="F231" t="inlineStr">
         <is>
           <t>must</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Incomplete</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A process is not available, not followed or not suitable for achieving the objective.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Performed</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>An undocumented or incompletely documented process is followed and indicators exist that it achieves its objective.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Managed</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A process achieving its objectives is followed. Process documentation and process implementation evidence are available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A standard process integrated into the overall system is followed. Dependencies on other processes are documented and suitable interfaces are created. Evidence exists that the process has been used sustainably and actively over an extended period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Predictable</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>An established process is followed. The effectiveness of the process is continually monitored by collecting key figures. Limit values are defined at which the process is considered to be insufficiently effective and requires adjustment. (Key Performance Indicators)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Optimizing</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>A predictable process with continual improvement as a major objective is followed. Improvement is actively advanced by dedicated resources.</t>
         </is>
       </c>
     </row>
@@ -6398,12 +5887,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>scores</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A process is not available, not followed or not suitable for achieving the objective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Performed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>An undocumented or incompletely documented process is followed and indicators exist that it achieves its objective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Managed</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A process achieving its objectives is followed. Process documentation and process implementation evidence are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A standard process integrated into the overall system is followed. Dependencies on other processes are documented and suitable interfaces are created. Evidence exists that the process has been used sustainably and actively over an extended period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Predictable</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>An established process is followed. The effectiveness of the process is continually monitored by collecting key figures. Limit values are defined at which the process is considered to be insufficiently effective and requires adjustment. (Key Performance Indicators)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Optimizing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A predictable process with continual improvement as a major objective is followed. Improvement is actively advanced by dedicated resources.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>implementation_groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>implementation_groups</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>ref_id</t>
         </is>
       </c>

--- a/tools/excel/tisax/tisax-v5.1.xlsx
+++ b/tools/excel/tisax/tisax-v5.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/titouanamelinedecadeville/Documents/ciso-assistant-community/tools/excel/tisax/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A01F43-2086-984C-9991-940D4FD5ADB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F82D25-0208-0F4D-A63D-FA37A33ADCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="392">
   <si>
     <t>type</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>Trusted Information Security Assessment Exchange</t>
   </si>
   <si>
     <t>description</t>
@@ -1952,39 +1949,39 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2002,15 +1999,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2018,7 +2015,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2034,47 +2031,47 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2089,10 +2086,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
         <v>32</v>
-      </c>
-      <c r="B1" t="s">
-        <v>33</v>
       </c>
       <c r="C1" t="s">
         <v>8</v>
@@ -2101,10 +2098,10 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2115,7 +2112,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2123,10 +2120,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2134,44 +2131,44 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
         <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>41</v>
-      </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2179,10 +2176,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
         <v>46</v>
-      </c>
-      <c r="E7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2190,27 +2187,27 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
         <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2218,61 +2215,61 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
         <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
         <v>55</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>56</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -2280,61 +2277,61 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
         <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -2342,61 +2339,61 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
         <v>63</v>
-      </c>
-      <c r="E18" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -2404,10 +2401,10 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
         <v>68</v>
-      </c>
-      <c r="E22" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -2415,44 +2412,44 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" t="s">
         <v>70</v>
-      </c>
-      <c r="E23" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -2460,44 +2457,44 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2505,44 +2502,44 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" t="s">
         <v>78</v>
-      </c>
-      <c r="E29" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2550,10 +2547,10 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" t="s">
         <v>82</v>
-      </c>
-      <c r="E32" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -2561,44 +2558,44 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" t="s">
         <v>84</v>
-      </c>
-      <c r="E33" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -2606,10 +2603,10 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" t="s">
         <v>88</v>
-      </c>
-      <c r="E36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -2617,44 +2614,44 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" t="s">
         <v>90</v>
-      </c>
-      <c r="E37" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2662,44 +2659,44 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" t="s">
         <v>94</v>
-      </c>
-      <c r="E40" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2707,10 +2704,10 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>97</v>
+      </c>
+      <c r="E43" t="s">
         <v>98</v>
-      </c>
-      <c r="E43" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -2718,61 +2715,61 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" t="s">
         <v>100</v>
-      </c>
-      <c r="E44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2780,10 +2777,10 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" t="s">
         <v>105</v>
-      </c>
-      <c r="D48" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2791,44 +2788,44 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
+        <v>106</v>
+      </c>
+      <c r="E49" t="s">
         <v>107</v>
-      </c>
-      <c r="E49" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -2836,44 +2833,44 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
+        <v>110</v>
+      </c>
+      <c r="E52" t="s">
         <v>111</v>
-      </c>
-      <c r="E52" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
@@ -2881,44 +2878,44 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
+        <v>114</v>
+      </c>
+      <c r="E55" t="s">
         <v>115</v>
-      </c>
-      <c r="E55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -2926,61 +2923,61 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" t="s">
         <v>119</v>
-      </c>
-      <c r="E58" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -2988,10 +2985,10 @@
         <v>3</v>
       </c>
       <c r="D62" t="s">
+        <v>123</v>
+      </c>
+      <c r="E62" t="s">
         <v>124</v>
-      </c>
-      <c r="E62" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
@@ -2999,10 +2996,10 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
+        <v>125</v>
+      </c>
+      <c r="D63" t="s">
         <v>126</v>
-      </c>
-      <c r="D63" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
@@ -3010,61 +3007,61 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
+        <v>127</v>
+      </c>
+      <c r="E64" t="s">
         <v>128</v>
-      </c>
-      <c r="E64" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E66" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
@@ -3072,10 +3069,10 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
@@ -3083,44 +3080,44 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
+        <v>133</v>
+      </c>
+      <c r="E69" t="s">
         <v>134</v>
-      </c>
-      <c r="E69" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E71" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
@@ -3128,44 +3125,44 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" t="s">
         <v>138</v>
-      </c>
-      <c r="E72" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F73" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
@@ -3173,61 +3170,61 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
+        <v>141</v>
+      </c>
+      <c r="E75" t="s">
         <v>142</v>
-      </c>
-      <c r="E75" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E76" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E77" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
@@ -3235,10 +3232,10 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
+        <v>146</v>
+      </c>
+      <c r="D79" t="s">
         <v>147</v>
-      </c>
-      <c r="D79" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
@@ -3246,10 +3243,10 @@
         <v>2</v>
       </c>
       <c r="C80" t="s">
+        <v>148</v>
+      </c>
+      <c r="E80" t="s">
         <v>149</v>
-      </c>
-      <c r="E80" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -3257,61 +3254,61 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
+        <v>150</v>
+      </c>
+      <c r="E81" t="s">
         <v>151</v>
-      </c>
-      <c r="E81" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B82">
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B83">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B84">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E84" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
@@ -3319,78 +3316,78 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
+        <v>155</v>
+      </c>
+      <c r="E85" t="s">
         <v>156</v>
-      </c>
-      <c r="E85" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B86">
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E86" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F86" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B87">
         <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E87" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B88">
         <v>4</v>
       </c>
       <c r="D88" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B89">
         <v>4</v>
       </c>
       <c r="D89" t="s">
+        <v>160</v>
+      </c>
+      <c r="E89" t="s">
         <v>161</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>162</v>
-      </c>
-      <c r="F89" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
@@ -3398,44 +3395,44 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
+        <v>163</v>
+      </c>
+      <c r="E90" t="s">
         <v>164</v>
-      </c>
-      <c r="E90" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B91">
         <v>4</v>
       </c>
       <c r="D91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E91" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F91" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B92">
         <v>4</v>
       </c>
       <c r="D92" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E92" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
@@ -3443,10 +3440,10 @@
         <v>2</v>
       </c>
       <c r="C93" t="s">
+        <v>167</v>
+      </c>
+      <c r="E93" t="s">
         <v>168</v>
-      </c>
-      <c r="E93" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
@@ -3454,78 +3451,78 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
+        <v>169</v>
+      </c>
+      <c r="E94" t="s">
         <v>170</v>
-      </c>
-      <c r="E94" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B95">
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E95" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B96">
         <v>4</v>
       </c>
       <c r="D96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E96" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F96" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B97">
         <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B98">
         <v>4</v>
       </c>
       <c r="D98" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E98" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F98" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
@@ -3533,10 +3530,10 @@
         <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E99" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
@@ -3544,10 +3541,10 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
@@ -3555,10 +3552,10 @@
         <v>2</v>
       </c>
       <c r="C101" t="s">
+        <v>177</v>
+      </c>
+      <c r="E101" t="s">
         <v>178</v>
-      </c>
-      <c r="E101" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
@@ -3566,61 +3563,61 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
+        <v>179</v>
+      </c>
+      <c r="E102" t="s">
         <v>180</v>
-      </c>
-      <c r="E102" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B103">
         <v>4</v>
       </c>
       <c r="D103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E103" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B104">
         <v>4</v>
       </c>
       <c r="D104" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E104" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F104" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B105">
         <v>4</v>
       </c>
       <c r="D105" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F105" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
@@ -3628,78 +3625,78 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
+        <v>184</v>
+      </c>
+      <c r="E106" t="s">
         <v>185</v>
-      </c>
-      <c r="E106" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B107">
         <v>4</v>
       </c>
       <c r="D107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E107" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F107" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B108">
         <v>4</v>
       </c>
       <c r="D108" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E108" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F108" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B109">
         <v>4</v>
       </c>
       <c r="D109" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E109" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F109" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B110">
         <v>4</v>
       </c>
       <c r="D110" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E110" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F110" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
@@ -3707,10 +3704,10 @@
         <v>2</v>
       </c>
       <c r="C111" t="s">
+        <v>190</v>
+      </c>
+      <c r="E111" t="s">
         <v>191</v>
-      </c>
-      <c r="E111" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
@@ -3718,61 +3715,61 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
+        <v>192</v>
+      </c>
+      <c r="E112" t="s">
         <v>193</v>
-      </c>
-      <c r="E112" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B113">
         <v>4</v>
       </c>
       <c r="D113" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E113" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F113" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B114">
         <v>4</v>
       </c>
       <c r="D114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F114" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B115">
         <v>4</v>
       </c>
       <c r="D115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F115" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
@@ -3780,44 +3777,44 @@
         <v>3</v>
       </c>
       <c r="C116" t="s">
+        <v>197</v>
+      </c>
+      <c r="E116" t="s">
         <v>198</v>
-      </c>
-      <c r="E116" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B117">
         <v>4</v>
       </c>
       <c r="D117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E117" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F117" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B118">
         <v>4</v>
       </c>
       <c r="D118" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E118" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F118" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
@@ -3825,44 +3822,44 @@
         <v>3</v>
       </c>
       <c r="C119" t="s">
+        <v>201</v>
+      </c>
+      <c r="E119" t="s">
         <v>202</v>
-      </c>
-      <c r="E119" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B120">
         <v>4</v>
       </c>
       <c r="D120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E120" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F120" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B121">
         <v>4</v>
       </c>
       <c r="D121" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E121" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F121" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
@@ -3870,78 +3867,78 @@
         <v>3</v>
       </c>
       <c r="C122" t="s">
+        <v>205</v>
+      </c>
+      <c r="E122" t="s">
         <v>206</v>
-      </c>
-      <c r="E122" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B123">
         <v>4</v>
       </c>
       <c r="D123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E123" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B124">
         <v>4</v>
       </c>
       <c r="D124" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E124" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F124" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="D125" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E125" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F125" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B126">
         <v>4</v>
       </c>
       <c r="D126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E126" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F126" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
@@ -3949,44 +3946,44 @@
         <v>3</v>
       </c>
       <c r="C127" t="s">
+        <v>211</v>
+      </c>
+      <c r="E127" t="s">
         <v>212</v>
-      </c>
-      <c r="E127" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B128">
         <v>4</v>
       </c>
       <c r="D128" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E128" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F128" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B129">
         <v>4</v>
       </c>
       <c r="D129" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E129" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F129" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
@@ -3994,44 +3991,44 @@
         <v>3</v>
       </c>
       <c r="C130" t="s">
+        <v>215</v>
+      </c>
+      <c r="E130" t="s">
         <v>216</v>
-      </c>
-      <c r="E130" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B131">
         <v>4</v>
       </c>
       <c r="D131" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E131" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F131" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B132">
         <v>4</v>
       </c>
       <c r="D132" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F132" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
@@ -4039,61 +4036,61 @@
         <v>3</v>
       </c>
       <c r="C133" t="s">
+        <v>219</v>
+      </c>
+      <c r="E133" t="s">
         <v>220</v>
-      </c>
-      <c r="E133" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B134">
         <v>4</v>
       </c>
       <c r="D134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E134" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B135">
         <v>4</v>
       </c>
       <c r="D135" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E135" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F135" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B136">
         <v>4</v>
       </c>
       <c r="D136" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E136" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F136" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
@@ -4101,10 +4098,10 @@
         <v>2</v>
       </c>
       <c r="C137" t="s">
+        <v>224</v>
+      </c>
+      <c r="E137" t="s">
         <v>225</v>
-      </c>
-      <c r="E137" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
@@ -4112,44 +4109,44 @@
         <v>3</v>
       </c>
       <c r="C138" t="s">
+        <v>226</v>
+      </c>
+      <c r="E138" t="s">
         <v>227</v>
-      </c>
-      <c r="E138" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B139">
         <v>4</v>
       </c>
       <c r="D139" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E139" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B140">
         <v>4</v>
       </c>
       <c r="D140" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E140" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F140" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
@@ -4157,61 +4154,61 @@
         <v>3</v>
       </c>
       <c r="C141" t="s">
+        <v>230</v>
+      </c>
+      <c r="E141" t="s">
         <v>231</v>
-      </c>
-      <c r="E141" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B142">
         <v>4</v>
       </c>
       <c r="D142" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E142" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F142" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B143">
         <v>4</v>
       </c>
       <c r="D143" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E143" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F143" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B144">
         <v>4</v>
       </c>
       <c r="D144" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E144" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
@@ -4219,44 +4216,44 @@
         <v>3</v>
       </c>
       <c r="C145" t="s">
+        <v>235</v>
+      </c>
+      <c r="E145" t="s">
         <v>236</v>
-      </c>
-      <c r="E145" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B146">
         <v>4</v>
       </c>
       <c r="D146" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E146" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B147">
         <v>4</v>
       </c>
       <c r="D147" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E147" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F147" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
@@ -4264,44 +4261,44 @@
         <v>3</v>
       </c>
       <c r="C148" t="s">
+        <v>239</v>
+      </c>
+      <c r="E148" t="s">
         <v>240</v>
-      </c>
-      <c r="E148" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B149">
         <v>4</v>
       </c>
       <c r="D149" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B150">
         <v>4</v>
       </c>
       <c r="D150" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E150" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F150" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
@@ -4309,10 +4306,10 @@
         <v>1</v>
       </c>
       <c r="C151" t="s">
+        <v>243</v>
+      </c>
+      <c r="D151" t="s">
         <v>244</v>
-      </c>
-      <c r="D151" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
@@ -4320,61 +4317,61 @@
         <v>2</v>
       </c>
       <c r="C152" t="s">
+        <v>245</v>
+      </c>
+      <c r="E152" t="s">
         <v>246</v>
-      </c>
-      <c r="E152" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B153">
         <v>3</v>
       </c>
       <c r="D153" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B154">
         <v>3</v>
       </c>
       <c r="D154" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E154" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F154" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B155">
         <v>3</v>
       </c>
       <c r="D155" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E155" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F155" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
@@ -4382,10 +4379,10 @@
         <v>3</v>
       </c>
       <c r="D156" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E156" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
@@ -4393,44 +4390,44 @@
         <v>2</v>
       </c>
       <c r="C157" t="s">
+        <v>251</v>
+      </c>
+      <c r="E157" t="s">
         <v>252</v>
-      </c>
-      <c r="E157" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B158">
         <v>3</v>
       </c>
       <c r="D158" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E158" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F158" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B159">
         <v>3</v>
       </c>
       <c r="D159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E159" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F159" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
@@ -4438,10 +4435,10 @@
         <v>1</v>
       </c>
       <c r="C160" t="s">
+        <v>255</v>
+      </c>
+      <c r="D160" t="s">
         <v>256</v>
-      </c>
-      <c r="D160" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
@@ -4449,44 +4446,44 @@
         <v>2</v>
       </c>
       <c r="C161" t="s">
+        <v>257</v>
+      </c>
+      <c r="E161" t="s">
         <v>258</v>
-      </c>
-      <c r="E161" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B162">
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F162" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B163">
         <v>3</v>
       </c>
       <c r="D163" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E163" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F163" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
@@ -4494,27 +4491,27 @@
         <v>2</v>
       </c>
       <c r="C164" t="s">
+        <v>261</v>
+      </c>
+      <c r="E164" t="s">
         <v>262</v>
-      </c>
-      <c r="E164" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B165">
         <v>3</v>
       </c>
       <c r="D165" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F165" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
@@ -4522,10 +4519,10 @@
         <v>1</v>
       </c>
       <c r="C166" t="s">
+        <v>264</v>
+      </c>
+      <c r="D166" t="s">
         <v>265</v>
-      </c>
-      <c r="D166" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
@@ -4533,10 +4530,10 @@
         <v>2</v>
       </c>
       <c r="C167" t="s">
+        <v>266</v>
+      </c>
+      <c r="E167" t="s">
         <v>267</v>
-      </c>
-      <c r="E167" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
@@ -4544,44 +4541,44 @@
         <v>3</v>
       </c>
       <c r="C168" t="s">
+        <v>268</v>
+      </c>
+      <c r="E168" t="s">
         <v>269</v>
-      </c>
-      <c r="E168" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B169">
         <v>4</v>
       </c>
       <c r="D169" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F169" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B170">
         <v>4</v>
       </c>
       <c r="D170" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E170" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
@@ -4589,44 +4586,44 @@
         <v>3</v>
       </c>
       <c r="C171" t="s">
+        <v>272</v>
+      </c>
+      <c r="E171" t="s">
         <v>273</v>
-      </c>
-      <c r="E171" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B172">
         <v>4</v>
       </c>
       <c r="D172" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E172" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F172" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B173">
         <v>4</v>
       </c>
       <c r="D173" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E173" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F173" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
@@ -4634,44 +4631,44 @@
         <v>3</v>
       </c>
       <c r="C174" t="s">
+        <v>276</v>
+      </c>
+      <c r="E174" t="s">
         <v>277</v>
-      </c>
-      <c r="E174" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B175">
         <v>4</v>
       </c>
       <c r="D175" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E175" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F175" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B176">
         <v>4</v>
       </c>
       <c r="D176" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E176" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F176" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
@@ -4679,61 +4676,61 @@
         <v>3</v>
       </c>
       <c r="C177" t="s">
+        <v>280</v>
+      </c>
+      <c r="E177" t="s">
         <v>281</v>
-      </c>
-      <c r="E177" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B178">
         <v>4</v>
       </c>
       <c r="D178" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E178" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F178" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B179">
         <v>4</v>
       </c>
       <c r="D179" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E179" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F179" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B180">
         <v>4</v>
       </c>
       <c r="D180" t="s">
+        <v>284</v>
+      </c>
+      <c r="E180" t="s">
         <v>285</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>286</v>
-      </c>
-      <c r="F180" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
@@ -4741,44 +4738,44 @@
         <v>3</v>
       </c>
       <c r="C181" t="s">
+        <v>287</v>
+      </c>
+      <c r="E181" t="s">
         <v>288</v>
-      </c>
-      <c r="E181" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B182">
         <v>4</v>
       </c>
       <c r="D182" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E182" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F182" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B183">
         <v>4</v>
       </c>
       <c r="D183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E183" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F183" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
@@ -4786,27 +4783,27 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
+        <v>291</v>
+      </c>
+      <c r="E184" t="s">
         <v>292</v>
-      </c>
-      <c r="E184" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B185">
         <v>4</v>
       </c>
       <c r="D185" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E185" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F185" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
@@ -4814,27 +4811,27 @@
         <v>3</v>
       </c>
       <c r="C186" t="s">
+        <v>294</v>
+      </c>
+      <c r="E186" t="s">
         <v>295</v>
-      </c>
-      <c r="E186" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B187">
         <v>4</v>
       </c>
       <c r="D187" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E187" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F187" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
@@ -4842,44 +4839,44 @@
         <v>3</v>
       </c>
       <c r="C188" t="s">
+        <v>297</v>
+      </c>
+      <c r="E188" t="s">
         <v>298</v>
-      </c>
-      <c r="E188" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B189">
         <v>4</v>
       </c>
       <c r="D189" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E189" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F189" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B190">
         <v>4</v>
       </c>
       <c r="D190" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E190" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F190" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
@@ -4887,10 +4884,10 @@
         <v>2</v>
       </c>
       <c r="C191" t="s">
+        <v>301</v>
+      </c>
+      <c r="E191" t="s">
         <v>302</v>
-      </c>
-      <c r="E191" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
@@ -4898,27 +4895,27 @@
         <v>3</v>
       </c>
       <c r="C192" t="s">
+        <v>303</v>
+      </c>
+      <c r="E192" t="s">
         <v>304</v>
-      </c>
-      <c r="E192" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B193">
         <v>4</v>
       </c>
       <c r="D193" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E193" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F193" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
@@ -4926,27 +4923,27 @@
         <v>3</v>
       </c>
       <c r="C194" t="s">
+        <v>306</v>
+      </c>
+      <c r="E194" t="s">
         <v>307</v>
-      </c>
-      <c r="E194" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B195">
         <v>4</v>
       </c>
       <c r="D195" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E195" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F195" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
@@ -4954,27 +4951,27 @@
         <v>3</v>
       </c>
       <c r="C196" t="s">
+        <v>309</v>
+      </c>
+      <c r="E196" t="s">
         <v>310</v>
-      </c>
-      <c r="E196" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B197">
         <v>4</v>
       </c>
       <c r="D197" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E197" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F197" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
@@ -4982,27 +4979,27 @@
         <v>3</v>
       </c>
       <c r="C198" t="s">
+        <v>312</v>
+      </c>
+      <c r="E198" t="s">
         <v>313</v>
-      </c>
-      <c r="E198" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B199">
         <v>4</v>
       </c>
       <c r="D199" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E199" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F199" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
@@ -5010,27 +5007,27 @@
         <v>3</v>
       </c>
       <c r="C200" t="s">
+        <v>315</v>
+      </c>
+      <c r="E200" t="s">
         <v>316</v>
-      </c>
-      <c r="E200" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B201">
         <v>4</v>
       </c>
       <c r="D201" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E201" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F201" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
@@ -5038,27 +5035,27 @@
         <v>3</v>
       </c>
       <c r="C202" t="s">
+        <v>318</v>
+      </c>
+      <c r="E202" t="s">
         <v>319</v>
-      </c>
-      <c r="E202" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B203">
         <v>4</v>
       </c>
       <c r="D203" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E203" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F203" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
@@ -5066,27 +5063,27 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
+        <v>321</v>
+      </c>
+      <c r="E204" t="s">
         <v>322</v>
-      </c>
-      <c r="E204" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B205">
         <v>4</v>
       </c>
       <c r="D205" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E205" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F205" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
@@ -5094,10 +5091,10 @@
         <v>2</v>
       </c>
       <c r="C206" t="s">
+        <v>324</v>
+      </c>
+      <c r="E206" t="s">
         <v>325</v>
-      </c>
-      <c r="E206" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
@@ -5105,27 +5102,27 @@
         <v>3</v>
       </c>
       <c r="C207" t="s">
+        <v>326</v>
+      </c>
+      <c r="E207" t="s">
         <v>327</v>
-      </c>
-      <c r="E207" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B208">
         <v>4</v>
       </c>
       <c r="D208" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E208" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F208" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
@@ -5133,27 +5130,27 @@
         <v>3</v>
       </c>
       <c r="C209" t="s">
+        <v>329</v>
+      </c>
+      <c r="E209" t="s">
         <v>330</v>
-      </c>
-      <c r="E209" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B210">
         <v>4</v>
       </c>
       <c r="D210" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E210" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F210" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
@@ -5161,10 +5158,10 @@
         <v>2</v>
       </c>
       <c r="C211" t="s">
+        <v>332</v>
+      </c>
+      <c r="E211" t="s">
         <v>333</v>
-      </c>
-      <c r="E211" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
@@ -5172,27 +5169,27 @@
         <v>3</v>
       </c>
       <c r="C212" t="s">
+        <v>334</v>
+      </c>
+      <c r="E212" t="s">
         <v>335</v>
-      </c>
-      <c r="E212" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B213">
         <v>4</v>
       </c>
       <c r="D213" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E213" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F213" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
@@ -5200,27 +5197,27 @@
         <v>3</v>
       </c>
       <c r="C214" t="s">
+        <v>337</v>
+      </c>
+      <c r="E214" t="s">
         <v>338</v>
-      </c>
-      <c r="E214" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B215">
         <v>4</v>
       </c>
       <c r="D215" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E215" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F215" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
@@ -5228,27 +5225,27 @@
         <v>3</v>
       </c>
       <c r="C216" t="s">
+        <v>340</v>
+      </c>
+      <c r="E216" t="s">
         <v>341</v>
-      </c>
-      <c r="E216" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B217">
         <v>4</v>
       </c>
       <c r="D217" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E217" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F217" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
@@ -5256,10 +5253,10 @@
         <v>2</v>
       </c>
       <c r="C218" t="s">
+        <v>343</v>
+      </c>
+      <c r="E218" t="s">
         <v>344</v>
-      </c>
-      <c r="E218" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
@@ -5267,27 +5264,27 @@
         <v>3</v>
       </c>
       <c r="C219" t="s">
+        <v>345</v>
+      </c>
+      <c r="E219" t="s">
         <v>346</v>
-      </c>
-      <c r="E219" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B220">
         <v>4</v>
       </c>
       <c r="D220" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E220" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F220" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
@@ -5295,27 +5292,27 @@
         <v>3</v>
       </c>
       <c r="C221" t="s">
+        <v>348</v>
+      </c>
+      <c r="E221" t="s">
         <v>349</v>
-      </c>
-      <c r="E221" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B222">
         <v>4</v>
       </c>
       <c r="D222" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E222" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F222" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
@@ -5323,10 +5320,10 @@
         <v>1</v>
       </c>
       <c r="C223" t="s">
+        <v>351</v>
+      </c>
+      <c r="D223" t="s">
         <v>352</v>
-      </c>
-      <c r="D223" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
@@ -5334,27 +5331,27 @@
         <v>2</v>
       </c>
       <c r="C224" t="s">
+        <v>353</v>
+      </c>
+      <c r="E224" t="s">
         <v>354</v>
-      </c>
-      <c r="E224" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B225">
         <v>3</v>
       </c>
       <c r="D225" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E225" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F225" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
@@ -5362,27 +5359,27 @@
         <v>2</v>
       </c>
       <c r="C226" t="s">
+        <v>356</v>
+      </c>
+      <c r="E226" t="s">
         <v>357</v>
-      </c>
-      <c r="E226" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B227">
         <v>3</v>
       </c>
       <c r="D227" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E227" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F227" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
@@ -5390,27 +5387,27 @@
         <v>2</v>
       </c>
       <c r="C228" t="s">
+        <v>359</v>
+      </c>
+      <c r="E228" t="s">
         <v>360</v>
-      </c>
-      <c r="E228" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B229">
         <v>3</v>
       </c>
       <c r="D229" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E229" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F229" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
@@ -5418,27 +5415,27 @@
         <v>2</v>
       </c>
       <c r="C230" t="s">
+        <v>362</v>
+      </c>
+      <c r="E230" t="s">
         <v>363</v>
-      </c>
-      <c r="E230" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B231">
         <v>3</v>
       </c>
       <c r="D231" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E231" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F231" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -5456,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5464,7 +5461,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -5479,13 +5476,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -5493,10 +5490,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" t="s">
         <v>367</v>
-      </c>
-      <c r="C2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -5504,10 +5501,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" t="s">
         <v>369</v>
-      </c>
-      <c r="C3" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -5515,10 +5512,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" t="s">
         <v>371</v>
-      </c>
-      <c r="C4" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5526,10 +5523,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" t="s">
         <v>373</v>
-      </c>
-      <c r="C5" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5537,10 +5534,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" t="s">
         <v>375</v>
-      </c>
-      <c r="C6" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -5548,10 +5545,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" t="s">
         <v>377</v>
-      </c>
-      <c r="C7" t="s">
-        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -5569,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5577,7 +5574,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5598,73 +5595,73 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C2" t="s">
         <v>379</v>
-      </c>
-      <c r="C2" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" t="s">
         <v>381</v>
-      </c>
-      <c r="C3" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" t="s">
         <v>383</v>
-      </c>
-      <c r="C4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" t="s">
         <v>385</v>
-      </c>
-      <c r="C5" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B6" t="s">
         <v>387</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>388</v>
-      </c>
-      <c r="C6" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" t="s">
         <v>390</v>
-      </c>
-      <c r="C7" t="s">
-        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/tisax/tisax-v5.1.xlsx
+++ b/tools/excel/tisax/tisax-v5.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/titouanamelinedecadeville/Documents/ciso-assistant-community/tools/excel/tisax/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericlaubacher/Documents/GitHub/ciso-assistant-community/tools/excel/tisax/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F82D25-0208-0F4D-A63D-FA37A33ADCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F853DD6F-D3E8-E648-AF53-C783D517EFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="392">
   <si>
     <t>type</t>
   </si>
@@ -1924,8 +1924,8 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">

--- a/tools/excel/tisax/tisax-v5.1.xlsx
+++ b/tools/excel/tisax/tisax-v5.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericlaubacher/Documents/GitHub/ciso-assistant-community/tools/excel/tisax/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F853DD6F-D3E8-E648-AF53-C783D517EFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A975B86A-C31A-A541-8D19-1D12D14C7742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -1561,17 +1561,24 @@
     <t>Protects physical prototypes which are classified as requiring protection. Prototypes include vehicles, components and parts. The owner of the intellectual property for the prototype is considered the owner of the prototype. The owner's commissioning department is responsible for classifying the protection need of a prototype. For prototypes classified as requiring high or very high protection, the minimum requirements for prototype protection must be applied.</t>
   </si>
   <si>
-    <t>Trusted Information Security Assessment Exchange v5.1</t>
+    <t>Trusted Information Security Assessment Exchange (TISAX) v5.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1597,8 +1604,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1903,6 +1911,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="255.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1993,6 +2004,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="255.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2030,7 +2044,7 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>391</v>
       </c>
     </row>
